--- a/reports/二级子公司C_现金流量表_2026-02.xlsx
+++ b/reports/二级子公司C_现金流量表_2026-02.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>70699200</v>
+        <v>70768876</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>141398400</v>
+        <v>141795134</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1373665</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>2741277</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>684904</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>1373045</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>344402</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>687249</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>273336</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>547735</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>206939</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>413300</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>136605</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>273409</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>103411</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>206828</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>68408</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>136709</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>171948</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>344394</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>86200</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>172061</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>54497</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>109243</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>181280</v>
+        <v>181759</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>362560</v>
+        <v>362665</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1359600</v>
+        <v>1354351</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>2719200</v>
+        <v>2714637</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>72240080</v>
+        <v>75809301</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>45320000</v>
+        <v>45454521</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>90640000</v>
+        <v>91000860</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>456900</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>912299</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>343176</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>687791</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>229180</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>457293</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>171072</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>342942</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>114878</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>229281</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>85823</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>171923</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>7704400</v>
+        <v>7742835</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>15408800</v>
+        <v>15470691</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>3806880</v>
+        <v>3789288</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>7613760</v>
+        <v>7580366</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1631520</v>
+        <v>1637671</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>3263040</v>
+        <v>3277060</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>58462800</v>
+        <v>60025344</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>13777280</v>
+        <v>15783957</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>103000</v>
+        <v>103509</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>206000</v>
+        <v>206727</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>824000</v>
+        <v>827620</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>1648000</v>
+        <v>1655265</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>515000</v>
+        <v>513249</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>1030000</v>
+        <v>1025707</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>927000</v>
+        <v>931129</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>6180000</v>
+        <v>6176963</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>12360000</v>
+        <v>12329687</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>824000</v>
+        <v>823075</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>1648000</v>
+        <v>1649904</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>4635000</v>
+        <v>4647135</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>9270000</v>
+        <v>9272431</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>206000</v>
+        <v>206990</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>412000</v>
+        <v>413775</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>6386000</v>
+        <v>6383953</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-5459000</v>
+        <v>-5452824</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>2060000</v>
+        <v>2059920</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>4120000</v>
+        <v>4128448</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>3090000</v>
+        <v>3080560</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>6180000</v>
+        <v>6175506</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>3090000</v>
+        <v>3102849</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>6180000</v>
+        <v>6192832</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>103000</v>
+        <v>102503</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>206000</v>
+        <v>205339</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>5253000</v>
+        <v>5242983</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2575000</v>
+        <v>2563070</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>5150000</v>
+        <v>5127426</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2575000</v>
+        <v>2584761</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>5150000</v>
+        <v>5172160</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>412000</v>
+        <v>410949</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>824000</v>
+        <v>820892</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>360500</v>
+        <v>360705</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>721000</v>
+        <v>719828</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>51500</v>
+        <v>51391</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>103000</v>
+        <v>103024</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>3038500</v>
+        <v>3025410</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>2214500</v>
+        <v>2217573</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>10532780</v>
+        <v>12548706</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4091,7 +4083,7 @@
       </c>
       <c r="F69" s="23" t="n"/>
       <c r="G69" s="20" t="n">
-        <v>11594000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" ht="18" customHeight="1">
@@ -4121,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>10532780</v>
+        <v>12548706</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
